--- a/output/screening/us_forged_shortlist.xlsx
+++ b/output/screening/us_forged_shortlist.xlsx
@@ -685,7 +685,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>f740c0125ee7e2823b63d650ffe6190fccd200f7</t>
+          <t>940e98dec8dc0cce89d85050e9ac598c69abebe8</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23T12:18:24+00:00</t>
+          <t>2026-08-28T06:50:02+00:00</t>
         </is>
       </c>
     </row>
@@ -23575,7 +23575,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="29" t="inlineStr">
         <is>
-          <t>명시 배제 8건 — config/known_exclusions.yaml (규칙 추론 아니라 사업자번호 명시 관리). 무엇을 왜 뺐는지 노출.</t>
+          <t>명시 배제 8건 — config/global_exclusions.yaml (규칙 추론 아니라 사업자번호 명시 관리). 무엇을 왜 뺐는지 노출.</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
